--- a/Excel-XLSX/UN-PLW.xlsx
+++ b/Excel-XLSX/UN-PLW.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>﻿"page"</t>
   </si>
@@ -63,25 +63,31 @@
     <t>asylum_seekers</t>
   </si>
   <si>
+    <t>returned_refugees</t>
+  </si>
+  <si>
     <t>idps</t>
   </si>
   <si>
+    <t>returned_idps</t>
+  </si>
+  <si>
+    <t>stateless</t>
+  </si>
+  <si>
+    <t>ooc</t>
+  </si>
+  <si>
     <t>oip</t>
   </si>
   <si>
-    <t>stateless</t>
-  </si>
-  <si>
     <t>hst</t>
   </si>
   <si>
-    <t>ooc</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
-    <t>w5X34x</t>
+    <t>pBS1y6</t>
   </si>
   <si>
     <t>2024</t>
@@ -526,7 +532,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <sheetData>
     <row r="1">
@@ -590,191 +596,215 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>31</v>
+      <c r="V3" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
